--- a/光伏配储项目/电价数据/2026/致远开关站.xlsx
+++ b/光伏配储项目/电价数据/2026/致远开关站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72372</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5649299999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51901</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21709</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07826999999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06420000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05309000000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03388</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03907</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01333</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14528</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21303</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21557</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11843</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00173</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.01051</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19386</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22473</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.01207</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12479</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19704</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.00593</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24322</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.46014</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76874</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6158899999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51705</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.59366</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5455800000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62029</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.35688</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.4355</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7587699999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.00047</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7466799999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52795</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51711</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51206</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6569700000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75463</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.18909</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09165999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04173</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.23064</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.15739</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58915</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23472</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16219</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23694</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.71117</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79506</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.81887</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.85077</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83568</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59922</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31205</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.49329</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.25491</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.08746</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.00358</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.20065</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.22362</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.00528</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22045</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15345</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21113</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19808</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24953</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22756</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.07532999999999999</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50506</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34415</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19512</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11342</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21109</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13503</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.03945000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06112</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17492</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03312</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07837000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19829</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16426</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20187</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.14936</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19325</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19731</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22557</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46891</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29226</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04513</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04029</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04003</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04494</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04546</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04672999999999999</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04806000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04656</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04690999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04812</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04656</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04872</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00209</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14713</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03763</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09889000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6644800000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10244</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04175</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04063</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03739</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04119</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04111</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04363</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04099</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04026</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0389</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03994</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0464</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20242</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14487</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33781</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3231</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40745</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17443</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17332</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14965</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16137</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16076</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23971</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21618</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.10837</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.19519</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78087</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92843</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90796</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.32009</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9310900000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63901</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22993</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.89002</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5818099999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37477</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06308</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82841</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.81062</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80738</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89352</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5283</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44503</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25213</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8801</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55179</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66664</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58977</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42856</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60203</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64397</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8653099999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.68375</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.6679299999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.77819</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24018</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.01177</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02825</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5057699999999999</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.7010299999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16475</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20124</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.08662</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28636</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.28095</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35808</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13625</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71216</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80629</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59117</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.07493000000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.00159</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.15275</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.12645</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.49054</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6093500000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46583</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68213</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32661</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.04536</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23731</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14663</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14935</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15631</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14484</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14386</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25908</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05451</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11377</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14263</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44187</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44627</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35075</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.10453</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.25274</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24531</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.00404</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18764</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09711</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.00546</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.15232</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.005809999999999999</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.00541</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.20443</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.00073</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.20234</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.21313</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.00514</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.00528</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.21696</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.00462</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.00519</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46234</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42836</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51747</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03217</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25001</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21216</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07564</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18548</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24517</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25402</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50896</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.78196</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45495</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47236</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.00214</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34509</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.02152</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7474500000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8802300000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48838</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13658</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1954</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.03093</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13146</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02174</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23814</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00331</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.01819</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23845</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6800499999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63846</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.64573</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5857100000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.80599</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46034</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48206</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49362</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47656</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46774</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5614199999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.17735</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.01059</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.01486</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.18625</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.03309</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10977</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48632</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6105700000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72793</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.71162</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.79665</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.56902</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.54423</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.88509</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.81225</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69811</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47508</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.49659</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49123</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.56302</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45666</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.28095</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15926</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04006000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45257</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01454</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18507</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36264</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23575</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23749</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04259</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.15247</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.06043</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17732</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25971</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15239</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06129</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01369</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.12537</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.03431</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.02126</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.15339</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.01749</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.03176</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35157</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19029</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18188</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.12981</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00143</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04141</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13674</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22179</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22237</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22747</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24041</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23182</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25114</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23386</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25245</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25864</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.25927</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25667</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21534</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23633</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21375</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18241</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.07772</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04489</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.22662</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.14919</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.14964</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21205</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19834</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16077</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15234</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18582</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11771</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18883</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15591</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20824</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.17972</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16748</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21806</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22526</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21462</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12731</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.18519</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00392</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16519</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.00449</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02944</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18554</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07781999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20862</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32634</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10559</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12454</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25758</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19115</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14329</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10815</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33222</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26218</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.03974</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.18151</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26836</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.05645</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52622</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.02091</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5527000000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45833</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.99713</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36904</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46813</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.47029</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19478</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46729</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56108</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46254</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55236</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5336799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52132</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.76678</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8103899999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55384</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44507</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37694</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26117</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24661</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13772</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.0321</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13648</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.009820000000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02258</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02001</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23566</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01356</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01722</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02987</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10393</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06597</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11891</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16745</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22255</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18106</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20692</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24843</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38095</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.76922</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21433</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.01105</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01282</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01475</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01538</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03606</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07623000000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00501</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00728</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.007990000000000001</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00192</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.03811999999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01257</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.00338</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.00497</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.00518</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22811</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.17952</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43159</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3976</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18378</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.16937</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14535</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17139</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15838</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08515</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10194</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04790999999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06798999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03713</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03756</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04493</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05906</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03384</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05577</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07023</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11194</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08474</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.15917</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14092</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08727</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21269</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09295999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.08928</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18459</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12724</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13887</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16255</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14348</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17802</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19671</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19779</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38201</v>
       </c>
     </row>
   </sheetData>
